--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,974 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130227835</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>637</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484708</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6781736</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130227776</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>637</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484729</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6781738</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130227969</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>637</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484699</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6781725</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130227893</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>637</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484703</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6781738</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130228031</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92596</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484756</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6781658</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera platser i skogen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130228362</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>637</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484730</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6781736</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130227844</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>637</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484705</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6781734</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130228152</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>637</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>484703</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6781704</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130227798</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>484708</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6781736</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>130227835</v>
       </c>
       <c r="B5" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130227776</v>
       </c>
       <c r="B6" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130227969</v>
       </c>
       <c r="B7" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227893</v>
+        <v>130228031</v>
       </c>
       <c r="B8" t="n">
-        <v>79162</v>
+        <v>92683</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>637</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484703</v>
+        <v>484756</v>
       </c>
       <c r="R8" t="n">
-        <v>6781738</v>
+        <v>6781658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera platser i skogen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228031</v>
+        <v>130227893</v>
       </c>
       <c r="B9" t="n">
-        <v>92596</v>
+        <v>79247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484756</v>
+        <v>484703</v>
       </c>
       <c r="R9" t="n">
-        <v>6781658</v>
+        <v>6781738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,12 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera platser i skogen</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1567,7 @@
         <v>130228362</v>
       </c>
       <c r="B10" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130227844</v>
+        <v>130228152</v>
       </c>
       <c r="B11" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484705</v>
+        <v>484703</v>
       </c>
       <c r="R11" t="n">
-        <v>6781734</v>
+        <v>6781704</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228152</v>
+        <v>130227844</v>
       </c>
       <c r="B12" t="n">
-        <v>79162</v>
+        <v>79247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484703</v>
+        <v>484705</v>
       </c>
       <c r="R12" t="n">
-        <v>6781704</v>
+        <v>6781734</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1888,7 +1888,7 @@
         <v>130227798</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>130227835</v>
       </c>
       <c r="B5" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130227776</v>
       </c>
       <c r="B6" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130227969</v>
       </c>
       <c r="B7" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130227893</v>
       </c>
       <c r="B8" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130228031</v>
       </c>
       <c r="B9" t="n">
-        <v>92683</v>
+        <v>92686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130228362</v>
       </c>
       <c r="B10" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130227844</v>
       </c>
       <c r="B11" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>130228152</v>
       </c>
       <c r="B12" t="n">
-        <v>79247</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>130227798</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>130227835</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130227776</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130227969</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130227893</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130228031</v>
       </c>
       <c r="B9" t="n">
-        <v>92686</v>
+        <v>92712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130228362</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130227844</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>130228152</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>130227798</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>130228031</v>
       </c>
       <c r="B9" t="n">
-        <v>92712</v>
+        <v>92713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>130228031</v>
       </c>
       <c r="B9" t="n">
-        <v>92713</v>
+        <v>92714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>130227835</v>
       </c>
       <c r="B5" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>130227776</v>
       </c>
       <c r="B6" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130227969</v>
       </c>
       <c r="B7" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227893</v>
+        <v>130228031</v>
       </c>
       <c r="B8" t="n">
-        <v>79276</v>
+        <v>92716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>637</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484703</v>
+        <v>484756</v>
       </c>
       <c r="R8" t="n">
-        <v>6781738</v>
+        <v>6781658</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera platser i skogen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228031</v>
+        <v>130227893</v>
       </c>
       <c r="B9" t="n">
-        <v>92714</v>
+        <v>79278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484756</v>
+        <v>484703</v>
       </c>
       <c r="R9" t="n">
-        <v>6781658</v>
+        <v>6781738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,12 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera platser i skogen</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1567,7 @@
         <v>130228362</v>
       </c>
       <c r="B10" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130227844</v>
       </c>
       <c r="B11" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>130228152</v>
       </c>
       <c r="B12" t="n">
-        <v>79276</v>
+        <v>79278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>130227798</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>130228031</v>
       </c>
       <c r="B8" t="n">
-        <v>92716</v>
+        <v>92720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -1345,32 +1345,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130228031</v>
+        <v>130227893</v>
       </c>
       <c r="B8" t="n">
-        <v>92720</v>
+        <v>79278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484756</v>
+        <v>484703</v>
       </c>
       <c r="R8" t="n">
-        <v>6781658</v>
+        <v>6781738</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera platser i skogen</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130227893</v>
+        <v>130228031</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>92720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>637</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,13 +1487,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484703</v>
+        <v>484756</v>
       </c>
       <c r="R9" t="n">
-        <v>6781738</v>
+        <v>6781658</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1532,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera platser i skogen</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111477816</v>
+        <v>107034821</v>
       </c>
       <c r="B2" t="n">
-        <v>77584</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallholn, Dlr</t>
+          <t>Kallholen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484733.489226101</v>
+        <v>484688</v>
       </c>
       <c r="R2" t="n">
-        <v>6781732.139435622</v>
+        <v>6781738</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Denna udda lokal hittade Anton Björk i vintras</t>
+          <t>På minst 75 träd! vissa rikligt beklädda med bålar långt upp på stammarna, framförallt på de större granarna intill vägen. Troligtvis gammal betesskog med lång trädkontinuitet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,12 +784,7 @@
         <v>111477805</v>
       </c>
       <c r="B3" t="n">
-        <v>77584</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484704.4829756203</v>
+        <v>484704</v>
       </c>
       <c r="R3" t="n">
-        <v>6781729.852835572</v>
+        <v>6781730</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,19 +852,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,38 +887,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129385573</v>
+        <v>111477816</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallholn, Kallholn, Dlr</t>
+          <t>Kallholn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -958,7 +931,7 @@
         <v>6781732</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +955,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Denna udda lokal hittade Anton Björk i vintras</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130227835</v>
+        <v>130227699</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484708</v>
+        <v>484736</v>
       </c>
       <c r="R5" t="n">
-        <v>6781736</v>
+        <v>6781757</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1103,7 @@
         <v>130227776</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130227969</v>
+        <v>130227835</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,13 +1242,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484699</v>
+        <v>484708</v>
       </c>
       <c r="R7" t="n">
-        <v>6781725</v>
+        <v>6781736</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227893</v>
+        <v>130227844</v>
       </c>
       <c r="B8" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484703</v>
+        <v>484705</v>
       </c>
       <c r="R8" t="n">
-        <v>6781738</v>
+        <v>6781734</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,7 +1384,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1394,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,32 +1421,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228031</v>
+        <v>130227881</v>
       </c>
       <c r="B9" t="n">
-        <v>92720</v>
+        <v>79394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,13 +1456,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484756</v>
+        <v>484703</v>
       </c>
       <c r="R9" t="n">
-        <v>6781658</v>
+        <v>6781738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,11 +1502,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera platser i skogen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,17 +1521,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130228362</v>
+        <v>130227888</v>
       </c>
       <c r="B10" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,17 +1559,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallholn, Kallholn, Dlr</t>
+          <t>Kallholen, Kallholen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484730</v>
+        <v>484683</v>
       </c>
       <c r="R10" t="n">
-        <v>6781736</v>
+        <v>6781738</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1598,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1608,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka ex på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,22 +1628,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130227844</v>
+        <v>130227969</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484705</v>
+        <v>484699</v>
       </c>
       <c r="R11" t="n">
-        <v>6781734</v>
+        <v>6781725</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,7 +1740,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1781,7 +1750,7 @@
         <v>130228152</v>
       </c>
       <c r="B12" t="n">
-        <v>79278</v>
+        <v>79394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,32 +1854,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130227798</v>
+        <v>130228362</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1920,7 +1889,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484708</v>
+        <v>484730</v>
       </c>
       <c r="R13" t="n">
         <v>6781736</v>
@@ -1955,7 +1924,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,7 +1934,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,53 +1961,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131955783</v>
+        <v>129385573</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallholn, Kallholn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484739</v>
+        <v>484733</v>
       </c>
       <c r="R14" t="n">
-        <v>6781629</v>
+        <v>6781732</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,22 +2026,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131955135</v>
+        <v>130228031</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,42 +2079,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallholn, Kallholn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484730</v>
+        <v>484756</v>
       </c>
       <c r="R15" t="n">
-        <v>6781730</v>
+        <v>6781658</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,22 +2133,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera platser i skogen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,57 +2173,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131955317</v>
+        <v>130227798</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallholn, Kallholn, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484731</v>
+        <v>484708</v>
       </c>
       <c r="R16" t="n">
-        <v>6781726</v>
+        <v>6781736</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2286,22 +2245,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,7 +2280,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2331,7 +2290,7 @@
         <v>131955166</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131955612</v>
+        <v>131955317</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,13 +2439,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484755</v>
+        <v>484731</v>
       </c>
       <c r="R18" t="n">
-        <v>6781621</v>
+        <v>6781726</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2515,7 +2474,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2525,7 +2484,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,45 +2504,45 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131955397</v>
+        <v>131955612</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2592,13 +2551,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484741</v>
+        <v>484755</v>
       </c>
       <c r="R19" t="n">
-        <v>6781703</v>
+        <v>6781621</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2586,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2596,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,10 +2616,346 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131955783</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>484739</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6781629</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131955135</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>484730</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6781730</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131955397</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kallholn, Kallholn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>484741</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6781703</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62761-2025 artfynd.xlsx
+++ b/artfynd/A 62761-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034821</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227699</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227776</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227835</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227844</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227881</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227888</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227969</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228152</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228362</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385573</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228031</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2284,6 +2359,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227798</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955166</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955317</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2620,6 +2710,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955612</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,6 +2827,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955783</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2844,6 +2944,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955135</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2956,8 +3061,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131955397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>